--- a/logs/nzd/raw/L2.xlsx
+++ b/logs/nzd/raw/L2.xlsx
@@ -1,124 +1,127 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="K:\ec\du\Surveys\Liquidity data\1. Data &amp; Analysis\2026\07\Web Tables\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{703E8F78-0148-4161-889C-5B038867741E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <workbookPr autoCompressPictures="1"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView tabRatio="600"/>
   </bookViews>
   <sheets>
-    <sheet name="Data" sheetId="1" r:id="rId1"/>
-    <sheet name="Table Description" sheetId="2" r:id="rId2"/>
-    <sheet name="Series Definitions" sheetId="3" r:id="rId3"/>
+    <sheet name="Data" sheetId="1" r:id="rId3"/>
+    <sheet name="Table Description" sheetId="2" r:id="rId4"/>
+    <sheet name="Series Definitions" sheetId="3" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="27">
   <si>
-    <t>Core funding</t>
+    <t xml:space="preserve">Core funding</t>
   </si>
   <si>
-    <t>A1. Total loans and advances</t>
+    <t xml:space="preserve">A1. Total loans and advances</t>
   </si>
   <si>
-    <t>Yes</t>
+    <t xml:space="preserve">Yes</t>
   </si>
   <si>
-    <t>NZDm</t>
+    <t xml:space="preserve">NZDm</t>
   </si>
   <si>
-    <t>LIQ.MBA8</t>
+    <t xml:space="preserve">LIQ.MBA8</t>
   </si>
   <si>
-    <t>A2. Core funding</t>
+    <t xml:space="preserve">A2. Core funding</t>
   </si>
   <si>
-    <t>LIQ.MBA5.ZZZZZR4</t>
+    <t xml:space="preserve">LIQ.MBA5.ZZZZZR4</t>
   </si>
   <si>
-    <t>A3. Core funding ratio</t>
+    <t xml:space="preserve">A3. Core funding ratio</t>
   </si>
   <si>
-    <t>%</t>
+    <t xml:space="preserve">%</t>
   </si>
   <si>
-    <t>LIQ.MBA7.ZZZZZR4</t>
+    <t xml:space="preserve">LIQ.MBA7.ZZZZZR4</t>
   </si>
   <si>
-    <t>Notes</t>
+    <t xml:space="preserve">Notes</t>
   </si>
   <si>
-    <t>Unit</t>
+    <t xml:space="preserve">Unit</t>
   </si>
   <si>
-    <t>Series Id</t>
+    <t xml:space="preserve">Series Id</t>
   </si>
   <si>
-    <t>Published By</t>
+    <t xml:space="preserve">Published By</t>
   </si>
   <si>
-    <t>Reserve Bank of New Zealand</t>
+    <t xml:space="preserve">Reserve Bank of New Zealand</t>
   </si>
   <si>
-    <t>Table</t>
+    <t xml:space="preserve">Table</t>
   </si>
   <si>
-    <t>Core funding ratio - L2</t>
+    <t xml:space="preserve">Core funding ratio - L2</t>
   </si>
   <si>
-    <t>Source</t>
+    <t xml:space="preserve">Source</t>
   </si>
   <si>
-    <t>Published Date</t>
+    <t xml:space="preserve">Published Date</t>
   </si>
   <si>
-    <t>General Notes:</t>
+    <t xml:space="preserve">General Notes:</t>
   </si>
   <si>
-    <t>Individual figures may not sum to the totals due to rounding</t>
+    <t xml:space="preserve">Individual figures may not sum to the totals due to rounding</t>
   </si>
   <si>
-    <t>Percentage changes are calculated on unrounded numbers</t>
+    <t xml:space="preserve">Percentage changes are calculated on unrounded numbers</t>
   </si>
   <si>
-    <t>You are free to copy, distribute and adapt these statistics subject to the conditions listed on our copyright page</t>
+    <t xml:space="preserve">You are free to copy, distribute and adapt these statistics subject to the conditions listed on our copyright page</t>
   </si>
   <si>
-    <t>Group</t>
+    <t xml:space="preserve">Group</t>
   </si>
   <si>
-    <t>Series</t>
+    <t xml:space="preserve">Series</t>
   </si>
   <si>
-    <t>Note</t>
+    <t xml:space="preserve">Note</t>
   </si>
   <si>
-    <t>An update to BS13 Liquidity policy applied from 1 January 2018 with the definition for Total loans and advances changed from the most recent Disclosure Statement figure to the figure for Total (Net) Loans and Advances as reported in the monthly Bank Balance Sheet Survey for the month that is two months prior to the BS13 reporting month.</t>
+    <t xml:space="preserve">An update to BS13 Liquidity policy applied from 1 January 2018 with the definition for Total loans and advances changed from the most recent Disclosure Statement figure to the figure for Total (Net) Loans and Advances as reported in the monthly Bank Balance Sheet Survey for the month that is two months prior to the BS13 reporting month.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
-    <numFmt numFmtId="169" formatCode="#,##0.0"/>
-    <numFmt numFmtId="174" formatCode="dd\ mmm\ yyyy"/>
-    <numFmt numFmtId="175" formatCode="mmm\ yyyy"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="14">
+    <numFmt numFmtId="165" formatCode="0.0"/>
+    <numFmt numFmtId="166" formatCode="0.000"/>
+    <numFmt numFmtId="167" formatCode="0.0000"/>
+    <numFmt numFmtId="168" formatCode="0.00000"/>
+    <numFmt numFmtId="169" formatCode="0.000000"/>
+    <numFmt numFmtId="170" formatCode="#,##0.0"/>
+    <numFmt numFmtId="171" formatCode="#,##0.000"/>
+    <numFmt numFmtId="172" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="173" formatCode="#,##0.00000"/>
+    <numFmt numFmtId="174" formatCode="#,##0.000000"/>
+    <numFmt numFmtId="175" formatCode="dd mmm yyyy"/>
+    <numFmt numFmtId="176" formatCode="mmm yyyy"/>
+    <numFmt numFmtId="177" formatCode="yyyy"/>
+    <numFmt numFmtId="178" formatCode="dd mmm"/>
   </numFmts>
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="34">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
-      <name val="Aptos Narrow"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -145,7 +148,18 @@
       <name val="Arial"/>
     </font>
     <font>
-      <u/>
+      <b/>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <u val="single"/>
+      <sz val="10"/>
+      <color indexed="12"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <u val="single"/>
       <sz val="10"/>
       <color indexed="12"/>
       <name val="Arial"/>
@@ -167,15 +181,91 @@
       <name val="Arial"/>
     </font>
     <font>
-      <u/>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <u val="single"/>
       <sz val="8"/>
       <color indexed="12"/>
       <name val="Consolas"/>
     </font>
     <font>
-      <u/>
+      <u val="single"/>
       <sz val="8"/>
       <color indexed="12"/>
+      <name val="Consolas"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Consolas"/>
     </font>
   </fonts>
@@ -184,7 +274,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="gray125"/>
+      <patternFill patternType="darkGray"/>
     </fill>
   </fills>
   <borders count="1">
@@ -197,399 +287,136 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+  <cellXfs count="34">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="169" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="174" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="168" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="170" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="171" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="172" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="173" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="174" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="175" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="175" fontId="27" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="175" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="28" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-  </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
-  <a:themeElements>
-    <a:clrScheme name="Office">
-      <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
-      </a:dk1>
-      <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
-      </a:lt1>
-      <a:dk2>
-        <a:srgbClr val="0E2841"/>
-      </a:dk2>
-      <a:lt2>
-        <a:srgbClr val="E8E8E8"/>
-      </a:lt2>
-      <a:accent1>
-        <a:srgbClr val="156082"/>
-      </a:accent1>
-      <a:accent2>
-        <a:srgbClr val="E97132"/>
-      </a:accent2>
-      <a:accent3>
-        <a:srgbClr val="196B24"/>
-      </a:accent3>
-      <a:accent4>
-        <a:srgbClr val="0F9ED5"/>
-      </a:accent4>
-      <a:accent5>
-        <a:srgbClr val="A02B93"/>
-      </a:accent5>
-      <a:accent6>
-        <a:srgbClr val="4EA72E"/>
-      </a:accent6>
-      <a:hlink>
-        <a:srgbClr val="467886"/>
-      </a:hlink>
-      <a:folHlink>
-        <a:srgbClr val="96607D"/>
-      </a:folHlink>
-    </a:clrScheme>
-    <a:fontScheme name="Office">
-      <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
-      </a:majorFont>
-      <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
-      </a:minorFont>
-    </a:fontScheme>
-    <a:fmtScheme name="Office">
-      <a:fillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-        </a:gradFill>
-      </a:fillStyleLst>
-      <a:lnStyleLst>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-      </a:lnStyleLst>
-      <a:effectStyleLst>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-      </a:effectStyleLst>
-      <a:bgFillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-        </a:gradFill>
-      </a:bgFillStyleLst>
-    </a:fmtScheme>
-  </a:themeElements>
-  <a:objectDefaults>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
-    </a:ext>
-  </a:extLst>
-</a:theme>
-</file>
-
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D201"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="13.7109375" customWidth="1" collapsed="1"/>
-    <col min="2" max="4" width="20.5703125" customWidth="1" collapsed="1"/>
+    <col min="1" max="1" width="13.671875" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" width="20.5078125" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="20.5078125" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="20.5078125" customWidth="1" collapsed="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B1" s="5" t="s">
+    <row r="1">
+      <c r="B1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="6" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="26.25" x14ac:dyDescent="0.25">
+    <row r="2">
       <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
@@ -600,7 +427,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3">
       <c r="A3" s="4" t="s">
         <v>10</v>
       </c>
@@ -608,7 +435,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4">
       <c r="A4" s="4" t="s">
         <v>11</v>
       </c>
@@ -622,2796 +449,2806 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5">
       <c r="A5" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="11" t="s">
+      <c r="B5" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="C5" s="31" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="11" t="s">
+      <c r="D5" s="31" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="10">
+    <row r="6">
+      <c r="A6" s="28">
         <v>40298</v>
       </c>
-      <c r="B6" s="7">
+      <c r="B6" s="16">
         <v>257714</v>
       </c>
-      <c r="C6" s="7">
+      <c r="C6" s="16">
         <v>202574</v>
       </c>
-      <c r="D6" s="8">
-        <v>78.599999999999994</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="10">
+      <c r="D6" s="17">
+        <v>78.6</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="28">
         <v>40329</v>
       </c>
-      <c r="B7" s="7">
+      <c r="B7" s="16">
         <v>257805</v>
       </c>
-      <c r="C7" s="7">
+      <c r="C7" s="16">
         <v>201632</v>
       </c>
-      <c r="D7" s="8">
+      <c r="D7" s="17">
         <v>78.2</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="10">
+    <row r="8">
+      <c r="A8" s="28">
         <v>40359</v>
       </c>
-      <c r="B8" s="7">
+      <c r="B8" s="16">
         <v>258432</v>
       </c>
-      <c r="C8" s="7">
+      <c r="C8" s="16">
         <v>201793</v>
       </c>
-      <c r="D8" s="8">
-        <v>78.099999999999994</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="10">
+      <c r="D8" s="17">
+        <v>78.1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="28">
         <v>40390</v>
       </c>
-      <c r="B9" s="7">
+      <c r="B9" s="16">
         <v>258432</v>
       </c>
-      <c r="C9" s="7">
+      <c r="C9" s="16">
         <v>200951</v>
       </c>
-      <c r="D9" s="8">
+      <c r="D9" s="17">
         <v>77.8</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="10">
+    <row r="10">
+      <c r="A10" s="28">
         <v>40421</v>
       </c>
-      <c r="B10" s="7">
+      <c r="B10" s="16">
         <v>259373</v>
       </c>
-      <c r="C10" s="7">
+      <c r="C10" s="16">
         <v>203858</v>
       </c>
-      <c r="D10" s="8">
-        <v>78.599999999999994</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="10">
+      <c r="D10" s="17">
+        <v>78.6</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="28">
         <v>40451</v>
       </c>
-      <c r="B11" s="7">
+      <c r="B11" s="16">
         <v>259666</v>
       </c>
-      <c r="C11" s="7">
+      <c r="C11" s="16">
         <v>205524</v>
       </c>
-      <c r="D11" s="8">
-        <v>79.099999999999994</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="10">
+      <c r="D11" s="17">
+        <v>79.1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="28">
         <v>40482</v>
       </c>
-      <c r="B12" s="7">
+      <c r="B12" s="16">
         <v>259666</v>
       </c>
-      <c r="C12" s="7">
+      <c r="C12" s="16">
         <v>207324</v>
       </c>
-      <c r="D12" s="8">
+      <c r="D12" s="17">
         <v>79.8</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="10">
+    <row r="13">
+      <c r="A13" s="28">
         <v>40512</v>
       </c>
-      <c r="B13" s="7">
+      <c r="B13" s="16">
         <v>259811</v>
       </c>
-      <c r="C13" s="7">
+      <c r="C13" s="16">
         <v>208926</v>
       </c>
-      <c r="D13" s="8">
-        <v>80.400000000000006</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="10">
+      <c r="D13" s="17">
+        <v>80.4</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="28">
         <v>40543</v>
       </c>
-      <c r="B14" s="7">
+      <c r="B14" s="16">
         <v>260334</v>
       </c>
-      <c r="C14" s="7">
+      <c r="C14" s="16">
         <v>211424</v>
       </c>
-      <c r="D14" s="8">
+      <c r="D14" s="17">
         <v>81.2</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="10">
+    <row r="15">
+      <c r="A15" s="28">
         <v>40574</v>
       </c>
-      <c r="B15" s="7">
+      <c r="B15" s="16">
         <v>260334</v>
       </c>
-      <c r="C15" s="7">
+      <c r="C15" s="16">
         <v>210261</v>
       </c>
-      <c r="D15" s="8">
+      <c r="D15" s="17">
         <v>80.8</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="10">
+    <row r="16">
+      <c r="A16" s="28">
         <v>40602</v>
       </c>
-      <c r="B16" s="7">
+      <c r="B16" s="16">
         <v>259904</v>
       </c>
-      <c r="C16" s="7">
+      <c r="C16" s="16">
         <v>212037</v>
       </c>
-      <c r="D16" s="8">
-        <v>81.599999999999994</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="10">
+      <c r="D16" s="17">
+        <v>81.6</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="28">
         <v>40633</v>
       </c>
-      <c r="B17" s="7">
+      <c r="B17" s="16">
         <v>259676</v>
       </c>
-      <c r="C17" s="7">
+      <c r="C17" s="16">
         <v>213559</v>
       </c>
-      <c r="D17" s="8">
+      <c r="D17" s="17">
         <v>82.2</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="10">
+    <row r="18">
+      <c r="A18" s="28">
         <v>40663</v>
       </c>
-      <c r="B18" s="7">
+      <c r="B18" s="16">
         <v>259676</v>
       </c>
-      <c r="C18" s="7">
+      <c r="C18" s="16">
         <v>214392</v>
       </c>
-      <c r="D18" s="8">
+      <c r="D18" s="17">
         <v>82.6</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="10">
+    <row r="19">
+      <c r="A19" s="28">
         <v>40694</v>
       </c>
-      <c r="B19" s="7">
+      <c r="B19" s="16">
         <v>259956</v>
       </c>
-      <c r="C19" s="7">
+      <c r="C19" s="16">
         <v>210733</v>
       </c>
-      <c r="D19" s="8">
-        <v>81.099999999999994</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="10">
+      <c r="D19" s="17">
+        <v>81.1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="28">
         <v>40724</v>
       </c>
-      <c r="B20" s="7">
+      <c r="B20" s="16">
         <v>259760</v>
       </c>
-      <c r="C20" s="7">
+      <c r="C20" s="16">
         <v>211269</v>
       </c>
-      <c r="D20" s="8">
+      <c r="D20" s="17">
         <v>81.3</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="10">
+    <row r="21">
+      <c r="A21" s="28">
         <v>40755</v>
       </c>
-      <c r="B21" s="7">
+      <c r="B21" s="16">
         <v>260609</v>
       </c>
-      <c r="C21" s="7">
+      <c r="C21" s="16">
         <v>212381</v>
       </c>
-      <c r="D21" s="8">
+      <c r="D21" s="17">
         <v>81.5</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="10">
+    <row r="22">
+      <c r="A22" s="28">
         <v>40786</v>
       </c>
-      <c r="B22" s="7">
+      <c r="B22" s="16">
         <v>261283</v>
       </c>
-      <c r="C22" s="7">
+      <c r="C22" s="16">
         <v>212186</v>
       </c>
-      <c r="D22" s="8">
+      <c r="D22" s="17">
         <v>81.2</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="10">
+    <row r="23">
+      <c r="A23" s="28">
         <v>40816</v>
       </c>
-      <c r="B23" s="7">
+      <c r="B23" s="16">
         <v>261283</v>
       </c>
-      <c r="C23" s="7">
+      <c r="C23" s="16">
         <v>214595</v>
       </c>
-      <c r="D23" s="8">
+      <c r="D23" s="17">
         <v>82.1</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="10">
+    <row r="24">
+      <c r="A24" s="28">
         <v>40847</v>
       </c>
-      <c r="B24" s="7">
+      <c r="B24" s="16">
         <v>261283</v>
       </c>
-      <c r="C24" s="7">
+      <c r="C24" s="16">
         <v>215107</v>
       </c>
-      <c r="D24" s="8">
+      <c r="D24" s="17">
         <v>82.3</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="10">
+    <row r="25">
+      <c r="A25" s="28">
         <v>40877</v>
       </c>
-      <c r="B25" s="7">
+      <c r="B25" s="16">
         <v>267242</v>
       </c>
-      <c r="C25" s="7">
+      <c r="C25" s="16">
         <v>222317</v>
       </c>
-      <c r="D25" s="8">
+      <c r="D25" s="17">
         <v>83.2</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="10">
+    <row r="26">
+      <c r="A26" s="28">
         <v>40908</v>
       </c>
-      <c r="B26" s="7">
+      <c r="B26" s="16">
         <v>268967</v>
       </c>
-      <c r="C26" s="7">
+      <c r="C26" s="16">
         <v>222767</v>
       </c>
-      <c r="D26" s="8">
+      <c r="D26" s="17">
         <v>82.8</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" s="10">
+    <row r="27">
+      <c r="A27" s="28">
         <v>40939</v>
       </c>
-      <c r="B27" s="7">
+      <c r="B27" s="16">
         <v>269421</v>
       </c>
-      <c r="C27" s="7">
+      <c r="C27" s="16">
         <v>220924</v>
       </c>
-      <c r="D27" s="8">
+      <c r="D27" s="17">
         <v>82</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" s="10">
+    <row r="28">
+      <c r="A28" s="28">
         <v>40968</v>
       </c>
-      <c r="B28" s="7">
+      <c r="B28" s="16">
         <v>269518</v>
       </c>
-      <c r="C28" s="7">
+      <c r="C28" s="16">
         <v>222197</v>
       </c>
-      <c r="D28" s="8">
+      <c r="D28" s="17">
         <v>82.4</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" s="10">
+    <row r="29">
+      <c r="A29" s="28">
         <v>40999</v>
       </c>
-      <c r="B29" s="7">
+      <c r="B29" s="16">
         <v>269723</v>
       </c>
-      <c r="C29" s="7">
+      <c r="C29" s="16">
         <v>226290</v>
       </c>
-      <c r="D29" s="8">
+      <c r="D29" s="17">
         <v>83.9</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" s="10">
+    <row r="30">
+      <c r="A30" s="28">
         <v>41029</v>
       </c>
-      <c r="B30" s="7">
+      <c r="B30" s="16">
         <v>269714</v>
       </c>
-      <c r="C30" s="7">
+      <c r="C30" s="16">
         <v>227262</v>
       </c>
-      <c r="D30" s="8">
+      <c r="D30" s="17">
         <v>84.3</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31" s="10">
+    <row r="31">
+      <c r="A31" s="28">
         <v>41060</v>
       </c>
-      <c r="B31" s="7">
+      <c r="B31" s="16">
         <v>272390</v>
       </c>
-      <c r="C31" s="7">
+      <c r="C31" s="16">
         <v>228380</v>
       </c>
-      <c r="D31" s="8">
+      <c r="D31" s="17">
         <v>83.8</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A32" s="10">
+    <row r="32">
+      <c r="A32" s="28">
         <v>41090</v>
       </c>
-      <c r="B32" s="7">
+      <c r="B32" s="16">
         <v>272348</v>
       </c>
-      <c r="C32" s="7">
+      <c r="C32" s="16">
         <v>227199</v>
       </c>
-      <c r="D32" s="8">
+      <c r="D32" s="17">
         <v>83.4</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A33" s="10">
+    <row r="33">
+      <c r="A33" s="28">
         <v>41121</v>
       </c>
-      <c r="B33" s="7">
+      <c r="B33" s="16">
         <v>272372</v>
       </c>
-      <c r="C33" s="7">
+      <c r="C33" s="16">
         <v>230157</v>
       </c>
-      <c r="D33" s="8">
+      <c r="D33" s="17">
         <v>84.5</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A34" s="10">
+    <row r="34">
+      <c r="A34" s="28">
         <v>41152</v>
       </c>
-      <c r="B34" s="7">
+      <c r="B34" s="16">
         <v>274107</v>
       </c>
-      <c r="C34" s="7">
+      <c r="C34" s="16">
         <v>231008</v>
       </c>
-      <c r="D34" s="8">
+      <c r="D34" s="17">
         <v>84.3</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A35" s="10">
+    <row r="35">
+      <c r="A35" s="28">
         <v>41182</v>
       </c>
-      <c r="B35" s="7">
+      <c r="B35" s="16">
         <v>274093</v>
       </c>
-      <c r="C35" s="7">
+      <c r="C35" s="16">
         <v>233696</v>
       </c>
-      <c r="D35" s="8">
+      <c r="D35" s="17">
         <v>85.3</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A36" s="10">
+    <row r="36">
+      <c r="A36" s="28">
         <v>41213</v>
       </c>
-      <c r="B36" s="7">
+      <c r="B36" s="16">
         <v>274312</v>
       </c>
-      <c r="C36" s="7">
+      <c r="C36" s="16">
         <v>235775</v>
       </c>
-      <c r="D36" s="8">
+      <c r="D36" s="17">
         <v>86</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A37" s="10">
+    <row r="37">
+      <c r="A37" s="28">
         <v>41243</v>
       </c>
-      <c r="B37" s="7">
+      <c r="B37" s="16">
         <v>277610</v>
       </c>
-      <c r="C37" s="7">
+      <c r="C37" s="16">
         <v>236555</v>
       </c>
-      <c r="D37" s="8">
+      <c r="D37" s="17">
         <v>85.2</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A38" s="10">
+    <row r="38">
+      <c r="A38" s="28">
         <v>41274</v>
       </c>
-      <c r="B38" s="7">
+      <c r="B38" s="16">
         <v>288196</v>
       </c>
-      <c r="C38" s="7">
+      <c r="C38" s="16">
         <v>246588</v>
       </c>
-      <c r="D38" s="8">
+      <c r="D38" s="17">
         <v>85.6</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A39" s="10">
+    <row r="39">
+      <c r="A39" s="28">
         <v>41305</v>
       </c>
-      <c r="B39" s="7">
+      <c r="B39" s="16">
         <v>287965</v>
       </c>
-      <c r="C39" s="7">
+      <c r="C39" s="16">
         <v>244263</v>
       </c>
-      <c r="D39" s="8">
+      <c r="D39" s="17">
         <v>84.8</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A40" s="10">
+    <row r="40">
+      <c r="A40" s="28">
         <v>41333</v>
       </c>
-      <c r="B40" s="7">
+      <c r="B40" s="16">
         <v>292070</v>
       </c>
-      <c r="C40" s="7">
+      <c r="C40" s="16">
         <v>245562</v>
       </c>
-      <c r="D40" s="8">
+      <c r="D40" s="17">
         <v>84.1</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A41" s="10">
+    <row r="41">
+      <c r="A41" s="28">
         <v>41364</v>
       </c>
-      <c r="B41" s="7">
+      <c r="B41" s="16">
         <v>292075</v>
       </c>
-      <c r="C41" s="7">
+      <c r="C41" s="16">
         <v>247685</v>
       </c>
-      <c r="D41" s="8">
+      <c r="D41" s="17">
         <v>84.8</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A42" s="10">
+    <row r="42">
+      <c r="A42" s="28">
         <v>41394</v>
       </c>
-      <c r="B42" s="7">
+      <c r="B42" s="16">
         <v>291946</v>
       </c>
-      <c r="C42" s="7">
+      <c r="C42" s="16">
         <v>250034</v>
       </c>
-      <c r="D42" s="8">
+      <c r="D42" s="17">
         <v>85.6</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A43" s="10">
+    <row r="43">
+      <c r="A43" s="28">
         <v>41425</v>
       </c>
-      <c r="B43" s="7">
+      <c r="B43" s="16">
         <v>294601</v>
       </c>
-      <c r="C43" s="7">
+      <c r="C43" s="16">
         <v>250043</v>
       </c>
-      <c r="D43" s="8">
+      <c r="D43" s="17">
         <v>84.9</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A44" s="10">
+    <row r="44">
+      <c r="A44" s="28">
         <v>41455</v>
       </c>
-      <c r="B44" s="7">
+      <c r="B44" s="16">
         <v>294733</v>
       </c>
-      <c r="C44" s="7">
+      <c r="C44" s="16">
         <v>250755</v>
       </c>
-      <c r="D44" s="8">
+      <c r="D44" s="17">
         <v>85.1</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A45" s="10">
+    <row r="45">
+      <c r="A45" s="28">
         <v>41486</v>
       </c>
-      <c r="B45" s="7">
+      <c r="B45" s="16">
         <v>295336</v>
       </c>
-      <c r="C45" s="7">
+      <c r="C45" s="16">
         <v>251876</v>
       </c>
-      <c r="D45" s="8">
+      <c r="D45" s="17">
         <v>85.3</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A46" s="10">
+    <row r="46">
+      <c r="A46" s="28">
         <v>41517</v>
       </c>
-      <c r="B46" s="7">
+      <c r="B46" s="16">
         <v>297512</v>
       </c>
-      <c r="C46" s="7">
+      <c r="C46" s="16">
         <v>253020</v>
       </c>
-      <c r="D46" s="8">
+      <c r="D46" s="17">
         <v>85</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A47" s="10">
+    <row r="47">
+      <c r="A47" s="28">
         <v>41547</v>
       </c>
-      <c r="B47" s="7">
+      <c r="B47" s="16">
         <v>298377</v>
       </c>
-      <c r="C47" s="7">
+      <c r="C47" s="16">
         <v>253453</v>
       </c>
-      <c r="D47" s="8">
+      <c r="D47" s="17">
         <v>84.9</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A48" s="10">
+    <row r="48">
+      <c r="A48" s="28">
         <v>41578</v>
       </c>
-      <c r="B48" s="7">
+      <c r="B48" s="16">
         <v>298377</v>
       </c>
-      <c r="C48" s="7">
+      <c r="C48" s="16">
         <v>253535</v>
       </c>
-      <c r="D48" s="8">
+      <c r="D48" s="17">
         <v>85</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A49" s="10">
+    <row r="49">
+      <c r="A49" s="28">
         <v>41608</v>
       </c>
-      <c r="B49" s="7">
+      <c r="B49" s="16">
         <v>302716</v>
       </c>
-      <c r="C49" s="7">
+      <c r="C49" s="16">
         <v>257328</v>
       </c>
-      <c r="D49" s="8">
+      <c r="D49" s="17">
         <v>85</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A50" s="10">
+    <row r="50">
+      <c r="A50" s="28">
         <v>41639</v>
       </c>
-      <c r="B50" s="7">
+      <c r="B50" s="16">
         <v>303420</v>
       </c>
-      <c r="C50" s="7">
+      <c r="C50" s="16">
         <v>259382</v>
       </c>
-      <c r="D50" s="8">
+      <c r="D50" s="17">
         <v>85.5</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A51" s="10">
+    <row r="51">
+      <c r="A51" s="28">
         <v>41670</v>
       </c>
-      <c r="B51" s="7">
+      <c r="B51" s="16">
         <v>303407</v>
       </c>
-      <c r="C51" s="7">
+      <c r="C51" s="16">
         <v>256939</v>
       </c>
-      <c r="D51" s="8">
+      <c r="D51" s="17">
         <v>84.7</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A52" s="10">
+    <row r="52">
+      <c r="A52" s="28">
         <v>41698</v>
       </c>
-      <c r="B52" s="7">
+      <c r="B52" s="16">
         <v>306582</v>
       </c>
-      <c r="C52" s="7">
+      <c r="C52" s="16">
         <v>259846</v>
       </c>
-      <c r="D52" s="8">
+      <c r="D52" s="17">
         <v>84.8</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A53" s="10">
+    <row r="53">
+      <c r="A53" s="28">
         <v>41729</v>
       </c>
-      <c r="B53" s="7">
+      <c r="B53" s="16">
         <v>306605</v>
       </c>
-      <c r="C53" s="7">
+      <c r="C53" s="16">
         <v>261830</v>
       </c>
-      <c r="D53" s="8">
+      <c r="D53" s="17">
         <v>85.4</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A54" s="10">
+    <row r="54">
+      <c r="A54" s="28">
         <v>41759</v>
       </c>
-      <c r="B54" s="7">
+      <c r="B54" s="16">
         <v>306578</v>
       </c>
-      <c r="C54" s="7">
+      <c r="C54" s="16">
         <v>264118</v>
       </c>
-      <c r="D54" s="8">
+      <c r="D54" s="17">
         <v>86.2</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A55" s="10">
+    <row r="55">
+      <c r="A55" s="28">
         <v>41790</v>
       </c>
-      <c r="B55" s="7">
+      <c r="B55" s="16">
         <v>310786</v>
       </c>
-      <c r="C55" s="7">
+      <c r="C55" s="16">
         <v>262400</v>
       </c>
-      <c r="D55" s="8">
+      <c r="D55" s="17">
         <v>84.4</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A56" s="10">
+    <row r="56">
+      <c r="A56" s="28">
         <v>41820</v>
       </c>
-      <c r="B56" s="7">
+      <c r="B56" s="16">
         <v>310834</v>
       </c>
-      <c r="C56" s="7">
+      <c r="C56" s="16">
         <v>262871</v>
       </c>
-      <c r="D56" s="8">
+      <c r="D56" s="17">
         <v>84.6</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A57" s="10">
+    <row r="57">
+      <c r="A57" s="28">
         <v>41851</v>
       </c>
-      <c r="B57" s="7">
+      <c r="B57" s="16">
         <v>310934</v>
       </c>
-      <c r="C57" s="7">
+      <c r="C57" s="16">
         <v>265786</v>
       </c>
-      <c r="D57" s="8">
+      <c r="D57" s="17">
         <v>85.5</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A58" s="10">
+    <row r="58">
+      <c r="A58" s="28">
         <v>41882</v>
       </c>
-      <c r="B58" s="7">
+      <c r="B58" s="16">
         <v>314565</v>
       </c>
-      <c r="C58" s="7">
+      <c r="C58" s="16">
         <v>264991</v>
       </c>
-      <c r="D58" s="8">
+      <c r="D58" s="17">
         <v>84.2</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A59" s="10">
+    <row r="59">
+      <c r="A59" s="28">
         <v>41912</v>
       </c>
-      <c r="B59" s="7">
+      <c r="B59" s="16">
         <v>314614</v>
       </c>
-      <c r="C59" s="7">
+      <c r="C59" s="16">
         <v>268943</v>
       </c>
-      <c r="D59" s="8">
+      <c r="D59" s="17">
         <v>85.5</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A60" s="10">
+    <row r="60">
+      <c r="A60" s="28">
         <v>41943</v>
       </c>
-      <c r="B60" s="7">
+      <c r="B60" s="16">
         <v>314676</v>
       </c>
-      <c r="C60" s="7">
+      <c r="C60" s="16">
         <v>271515</v>
       </c>
-      <c r="D60" s="8">
+      <c r="D60" s="17">
         <v>86.3</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A61" s="10">
+    <row r="61">
+      <c r="A61" s="28">
         <v>41973</v>
       </c>
-      <c r="B61" s="7">
+      <c r="B61" s="16">
         <v>318114</v>
       </c>
-      <c r="C61" s="7">
+      <c r="C61" s="16">
         <v>274121</v>
       </c>
-      <c r="D61" s="8">
+      <c r="D61" s="17">
         <v>86.2</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A62" s="10">
+    <row r="62">
+      <c r="A62" s="28">
         <v>42004</v>
       </c>
-      <c r="B62" s="7">
+      <c r="B62" s="16">
         <v>319554</v>
       </c>
-      <c r="C62" s="7">
+      <c r="C62" s="16">
         <v>275893</v>
       </c>
-      <c r="D62" s="8">
+      <c r="D62" s="17">
         <v>86.3</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A63" s="10">
+    <row r="63">
+      <c r="A63" s="28">
         <v>42035</v>
       </c>
-      <c r="B63" s="7">
+      <c r="B63" s="16">
         <v>319758</v>
       </c>
-      <c r="C63" s="7">
+      <c r="C63" s="16">
         <v>276888</v>
       </c>
-      <c r="D63" s="8">
+      <c r="D63" s="17">
         <v>86.6</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A64" s="10">
+    <row r="64">
+      <c r="A64" s="28">
         <v>42063</v>
       </c>
-      <c r="B64" s="7">
+      <c r="B64" s="16">
         <v>324986</v>
       </c>
-      <c r="C64" s="7">
+      <c r="C64" s="16">
         <v>277519</v>
       </c>
-      <c r="D64" s="8">
+      <c r="D64" s="17">
         <v>85.4</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A65" s="10">
+    <row r="65">
+      <c r="A65" s="28">
         <v>42094</v>
       </c>
-      <c r="B65" s="7">
+      <c r="B65" s="16">
         <v>325186</v>
       </c>
-      <c r="C65" s="7">
+      <c r="C65" s="16">
         <v>280843</v>
       </c>
-      <c r="D65" s="8">
+      <c r="D65" s="17">
         <v>86.4</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A66" s="10">
+    <row r="66">
+      <c r="A66" s="28">
         <v>42124</v>
       </c>
-      <c r="B66" s="7">
+      <c r="B66" s="16">
         <v>325278</v>
       </c>
-      <c r="C66" s="7">
+      <c r="C66" s="16">
         <v>281004</v>
       </c>
-      <c r="D66" s="8">
+      <c r="D66" s="17">
         <v>86.4</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A67" s="10">
+    <row r="67">
+      <c r="A67" s="28">
         <v>42155</v>
       </c>
-      <c r="B67" s="7">
+      <c r="B67" s="16">
         <v>331308</v>
       </c>
-      <c r="C67" s="7">
+      <c r="C67" s="16">
         <v>285579</v>
       </c>
-      <c r="D67" s="8">
+      <c r="D67" s="17">
         <v>86.2</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A68" s="10">
+    <row r="68">
+      <c r="A68" s="28">
         <v>42185</v>
       </c>
-      <c r="B68" s="7">
+      <c r="B68" s="16">
         <v>331490</v>
       </c>
-      <c r="C68" s="7">
+      <c r="C68" s="16">
         <v>287937</v>
       </c>
-      <c r="D68" s="8">
+      <c r="D68" s="17">
         <v>86.9</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A69" s="10">
+    <row r="69">
+      <c r="A69" s="28">
         <v>42216</v>
       </c>
-      <c r="B69" s="7">
+      <c r="B69" s="16">
         <v>331592</v>
       </c>
-      <c r="C69" s="7">
+      <c r="C69" s="16">
         <v>291650</v>
       </c>
-      <c r="D69" s="8">
+      <c r="D69" s="17">
         <v>88</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A70" s="10">
+    <row r="70">
+      <c r="A70" s="28">
         <v>42247</v>
       </c>
-      <c r="B70" s="7">
+      <c r="B70" s="16">
         <v>340339</v>
       </c>
-      <c r="C70" s="7">
+      <c r="C70" s="16">
         <v>294349</v>
       </c>
-      <c r="D70" s="8">
+      <c r="D70" s="17">
         <v>86.5</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A71" s="10">
+    <row r="71">
+      <c r="A71" s="28">
         <v>42277</v>
       </c>
-      <c r="B71" s="7">
+      <c r="B71" s="16">
         <v>340658</v>
       </c>
-      <c r="C71" s="7">
+      <c r="C71" s="16">
         <v>296726</v>
       </c>
-      <c r="D71" s="8">
+      <c r="D71" s="17">
         <v>87.1</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A72" s="10">
+    <row r="72">
+      <c r="A72" s="28">
         <v>42308</v>
       </c>
-      <c r="B72" s="7">
+      <c r="B72" s="16">
         <v>340658</v>
       </c>
-      <c r="C72" s="7">
+      <c r="C72" s="16">
         <v>293369</v>
       </c>
-      <c r="D72" s="8">
+      <c r="D72" s="17">
         <v>86.1</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A73" s="10">
+    <row r="73">
+      <c r="A73" s="28">
         <v>42338</v>
       </c>
-      <c r="B73" s="7">
+      <c r="B73" s="16">
         <v>345913</v>
       </c>
-      <c r="C73" s="7">
+      <c r="C73" s="16">
         <v>297393</v>
       </c>
-      <c r="D73" s="8">
+      <c r="D73" s="17">
         <v>86</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A74" s="10">
+    <row r="74">
+      <c r="A74" s="28">
         <v>42369</v>
       </c>
-      <c r="B74" s="7">
+      <c r="B74" s="16">
         <v>347189</v>
       </c>
-      <c r="C74" s="7">
+      <c r="C74" s="16">
         <v>298055</v>
       </c>
-      <c r="D74" s="8">
+      <c r="D74" s="17">
         <v>85.8</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A75" s="10">
+    <row r="75">
+      <c r="A75" s="28">
         <v>42400</v>
       </c>
-      <c r="B75" s="7">
+      <c r="B75" s="16">
         <v>347798</v>
       </c>
-      <c r="C75" s="7">
+      <c r="C75" s="16">
         <v>298713</v>
       </c>
-      <c r="D75" s="8">
+      <c r="D75" s="17">
         <v>85.9</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A76" s="10">
+    <row r="76">
+      <c r="A76" s="28">
         <v>42429</v>
       </c>
-      <c r="B76" s="7">
+      <c r="B76" s="16">
         <v>354700</v>
       </c>
-      <c r="C76" s="7">
+      <c r="C76" s="16">
         <v>303774</v>
       </c>
-      <c r="D76" s="8">
+      <c r="D76" s="17">
         <v>85.6</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A77" s="10">
+    <row r="77">
+      <c r="A77" s="28">
         <v>42460</v>
       </c>
-      <c r="B77" s="7">
+      <c r="B77" s="16">
         <v>354813</v>
       </c>
-      <c r="C77" s="7">
+      <c r="C77" s="16">
         <v>305553</v>
       </c>
-      <c r="D77" s="8">
+      <c r="D77" s="17">
         <v>86.1</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A78" s="10">
+    <row r="78">
+      <c r="A78" s="28">
         <v>42490</v>
       </c>
-      <c r="B78" s="7">
+      <c r="B78" s="16">
         <v>355016</v>
       </c>
-      <c r="C78" s="7">
+      <c r="C78" s="16">
         <v>307333</v>
       </c>
-      <c r="D78" s="8">
+      <c r="D78" s="17">
         <v>86.6</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A79" s="10">
+    <row r="79">
+      <c r="A79" s="28">
         <v>42521</v>
       </c>
-      <c r="B79" s="7">
+      <c r="B79" s="16">
         <v>361933</v>
       </c>
-      <c r="C79" s="7">
+      <c r="C79" s="16">
         <v>309284</v>
       </c>
-      <c r="D79" s="8">
+      <c r="D79" s="17">
         <v>85.5</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A80" s="10">
+    <row r="80">
+      <c r="A80" s="28">
         <v>42551</v>
       </c>
-      <c r="B80" s="7">
+      <c r="B80" s="16">
         <v>362024</v>
       </c>
-      <c r="C80" s="7">
+      <c r="C80" s="16">
         <v>313219</v>
       </c>
-      <c r="D80" s="8">
+      <c r="D80" s="17">
         <v>86.5</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A81" s="10">
+    <row r="81">
+      <c r="A81" s="28">
         <v>42582</v>
       </c>
-      <c r="B81" s="7">
+      <c r="B81" s="16">
         <v>362113</v>
       </c>
-      <c r="C81" s="7">
+      <c r="C81" s="16">
         <v>317020</v>
       </c>
-      <c r="D81" s="8">
+      <c r="D81" s="17">
         <v>87.5</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A82" s="10">
+    <row r="82">
+      <c r="A82" s="28">
         <v>42613</v>
       </c>
-      <c r="B82" s="7">
+      <c r="B82" s="16">
         <v>370964</v>
       </c>
-      <c r="C82" s="7">
+      <c r="C82" s="16">
         <v>317405</v>
       </c>
-      <c r="D82" s="8">
+      <c r="D82" s="17">
         <v>85.6</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A83" s="10">
+    <row r="83">
+      <c r="A83" s="28">
         <v>42643</v>
       </c>
-      <c r="B83" s="7">
+      <c r="B83" s="16">
         <v>370974</v>
       </c>
-      <c r="C83" s="7">
+      <c r="C83" s="16">
         <v>320041</v>
       </c>
-      <c r="D83" s="8">
+      <c r="D83" s="17">
         <v>86.3</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A84" s="10">
+    <row r="84">
+      <c r="A84" s="28">
         <v>42674</v>
       </c>
-      <c r="B84" s="7">
+      <c r="B84" s="16">
         <v>371101</v>
       </c>
-      <c r="C84" s="7">
+      <c r="C84" s="16">
         <v>323046</v>
       </c>
-      <c r="D84" s="8">
+      <c r="D84" s="17">
         <v>87.1</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A85" s="10">
+    <row r="85">
+      <c r="A85" s="28">
         <v>42704</v>
       </c>
-      <c r="B85" s="7">
+      <c r="B85" s="16">
         <v>375896</v>
       </c>
-      <c r="C85" s="7">
+      <c r="C85" s="16">
         <v>325040</v>
       </c>
-      <c r="D85" s="8">
+      <c r="D85" s="17">
         <v>86.5</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A86" s="10">
+    <row r="86">
+      <c r="A86" s="28">
         <v>42735</v>
       </c>
-      <c r="B86" s="7">
+      <c r="B86" s="16">
         <v>379164</v>
       </c>
-      <c r="C86" s="7">
+      <c r="C86" s="16">
         <v>330510</v>
       </c>
-      <c r="D86" s="8">
+      <c r="D86" s="17">
         <v>87.2</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A87" s="10">
+    <row r="87">
+      <c r="A87" s="28">
         <v>42766</v>
       </c>
-      <c r="B87" s="7">
+      <c r="B87" s="16">
         <v>379286</v>
       </c>
-      <c r="C87" s="7">
+      <c r="C87" s="16">
         <v>329816</v>
       </c>
-      <c r="D87" s="8">
+      <c r="D87" s="17">
         <v>87</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A88" s="10">
+    <row r="88">
+      <c r="A88" s="28">
         <v>42794</v>
       </c>
-      <c r="B88" s="7">
+      <c r="B88" s="16">
         <v>385548</v>
       </c>
-      <c r="C88" s="7">
+      <c r="C88" s="16">
         <v>333781</v>
       </c>
-      <c r="D88" s="8">
+      <c r="D88" s="17">
         <v>86.6</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A89" s="10">
+    <row r="89">
+      <c r="A89" s="28">
         <v>42825</v>
       </c>
-      <c r="B89" s="7">
+      <c r="B89" s="16">
         <v>385965</v>
       </c>
-      <c r="C89" s="7">
+      <c r="C89" s="16">
         <v>338112</v>
       </c>
-      <c r="D89" s="8">
+      <c r="D89" s="17">
         <v>87.6</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A90" s="10">
+    <row r="90">
+      <c r="A90" s="28">
         <v>42855</v>
       </c>
-      <c r="B90" s="7">
+      <c r="B90" s="16">
         <v>385930</v>
       </c>
-      <c r="C90" s="7">
+      <c r="C90" s="16">
         <v>340931</v>
       </c>
-      <c r="D90" s="8">
+      <c r="D90" s="17">
         <v>88.3</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A91" s="10">
+    <row r="91">
+      <c r="A91" s="28">
         <v>42886</v>
       </c>
-      <c r="B91" s="7">
+      <c r="B91" s="16">
         <v>391030</v>
       </c>
-      <c r="C91" s="7">
+      <c r="C91" s="16">
         <v>338610</v>
       </c>
-      <c r="D91" s="8">
+      <c r="D91" s="17">
         <v>86.6</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A92" s="10">
+    <row r="92">
+      <c r="A92" s="28">
         <v>42916</v>
       </c>
-      <c r="B92" s="7">
+      <c r="B92" s="16">
         <v>391249</v>
       </c>
-      <c r="C92" s="7">
+      <c r="C92" s="16">
         <v>337770</v>
       </c>
-      <c r="D92" s="8">
+      <c r="D92" s="17">
         <v>86.3</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A93" s="10">
+    <row r="93">
+      <c r="A93" s="28">
         <v>42947</v>
       </c>
-      <c r="B93" s="7">
+      <c r="B93" s="16">
         <v>391287</v>
       </c>
-      <c r="C93" s="7">
+      <c r="C93" s="16">
         <v>343578</v>
       </c>
-      <c r="D93" s="8">
+      <c r="D93" s="17">
         <v>87.8</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A94" s="10">
+    <row r="94">
+      <c r="A94" s="28">
         <v>42978</v>
       </c>
-      <c r="B94" s="7">
+      <c r="B94" s="16">
         <v>396818</v>
       </c>
-      <c r="C94" s="7">
+      <c r="C94" s="16">
         <v>344633</v>
       </c>
-      <c r="D94" s="8">
+      <c r="D94" s="17">
         <v>86.8</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A95" s="10">
+    <row r="95">
+      <c r="A95" s="28">
         <v>43008</v>
       </c>
-      <c r="B95" s="7">
+      <c r="B95" s="16">
         <v>396945</v>
       </c>
-      <c r="C95" s="7">
+      <c r="C95" s="16">
         <v>347702</v>
       </c>
-      <c r="D95" s="8">
+      <c r="D95" s="17">
         <v>87.6</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A96" s="10">
+    <row r="96">
+      <c r="A96" s="28">
         <v>43039</v>
       </c>
-      <c r="B96" s="7">
+      <c r="B96" s="16">
         <v>397083</v>
       </c>
-      <c r="C96" s="7">
+      <c r="C96" s="16">
         <v>351056</v>
       </c>
-      <c r="D96" s="8">
+      <c r="D96" s="17">
         <v>88.4</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A97" s="10">
+    <row r="97">
+      <c r="A97" s="28">
         <v>43069</v>
       </c>
-      <c r="B97" s="7">
+      <c r="B97" s="16">
         <v>401095</v>
       </c>
-      <c r="C97" s="7">
+      <c r="C97" s="16">
         <v>354151</v>
       </c>
-      <c r="D97" s="8">
+      <c r="D97" s="17">
         <v>88.3</v>
       </c>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A98" s="10">
+    <row r="98">
+      <c r="A98" s="28">
         <v>43100</v>
       </c>
-      <c r="B98" s="7">
+      <c r="B98" s="16">
         <v>402440</v>
       </c>
-      <c r="C98" s="7">
+      <c r="C98" s="16">
         <v>356901</v>
       </c>
-      <c r="D98" s="8">
+      <c r="D98" s="17">
         <v>88.7</v>
       </c>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A99" s="10">
+    <row r="99">
+      <c r="A99" s="28">
         <v>43131</v>
       </c>
-      <c r="B99" s="7">
+      <c r="B99" s="16">
         <v>406651</v>
       </c>
-      <c r="C99" s="7">
+      <c r="C99" s="16">
         <v>357731</v>
       </c>
-      <c r="D99" s="8">
+      <c r="D99" s="17">
         <v>88</v>
       </c>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A100" s="10">
+    <row r="100">
+      <c r="A100" s="28">
         <v>43159</v>
       </c>
-      <c r="B100" s="7">
+      <c r="B100" s="16">
         <v>408082</v>
       </c>
-      <c r="C100" s="7">
+      <c r="C100" s="16">
         <v>358066</v>
       </c>
-      <c r="D100" s="8">
+      <c r="D100" s="17">
         <v>87.7</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A101" s="10">
+    <row r="101">
+      <c r="A101" s="28">
         <v>43190</v>
       </c>
-      <c r="B101" s="7">
+      <c r="B101" s="16">
         <v>408701</v>
       </c>
-      <c r="C101" s="7">
+      <c r="C101" s="16">
         <v>361322</v>
       </c>
-      <c r="D101" s="8">
+      <c r="D101" s="17">
         <v>88.4</v>
       </c>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A102" s="10">
+    <row r="102">
+      <c r="A102" s="28">
         <v>43220</v>
       </c>
-      <c r="B102" s="7">
+      <c r="B102" s="16">
         <v>409997</v>
       </c>
-      <c r="C102" s="7">
+      <c r="C102" s="16">
         <v>364200</v>
       </c>
-      <c r="D102" s="8">
+      <c r="D102" s="17">
         <v>88.8</v>
       </c>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A103" s="10">
+    <row r="103">
+      <c r="A103" s="28">
         <v>43251</v>
       </c>
-      <c r="B103" s="7">
+      <c r="B103" s="16">
         <v>411884</v>
       </c>
-      <c r="C103" s="7">
+      <c r="C103" s="16">
         <v>362851</v>
       </c>
-      <c r="D103" s="8">
+      <c r="D103" s="17">
         <v>88.1</v>
       </c>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A104" s="10">
+    <row r="104">
+      <c r="A104" s="28">
         <v>43281</v>
       </c>
-      <c r="B104" s="7">
+      <c r="B104" s="16">
         <v>414009</v>
       </c>
-      <c r="C104" s="7">
+      <c r="C104" s="16">
         <v>364885</v>
       </c>
-      <c r="D104" s="8">
+      <c r="D104" s="17">
         <v>88.1</v>
       </c>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A105" s="10">
+    <row r="105">
+      <c r="A105" s="28">
         <v>43312</v>
       </c>
-      <c r="B105" s="7">
+      <c r="B105" s="16">
         <v>416143</v>
       </c>
-      <c r="C105" s="7">
+      <c r="C105" s="16">
         <v>368950</v>
       </c>
-      <c r="D105" s="8">
+      <c r="D105" s="17">
         <v>88.7</v>
       </c>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A106" s="10">
+    <row r="106">
+      <c r="A106" s="28">
         <v>43343</v>
       </c>
-      <c r="B106" s="7">
+      <c r="B106" s="16">
         <v>418765</v>
       </c>
-      <c r="C106" s="7">
+      <c r="C106" s="16">
         <v>368490</v>
       </c>
-      <c r="D106" s="8">
+      <c r="D106" s="17">
         <v>88</v>
       </c>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A107" s="10">
+    <row r="107">
+      <c r="A107" s="28">
         <v>43373</v>
       </c>
-      <c r="B107" s="7">
+      <c r="B107" s="16">
         <v>418496</v>
       </c>
-      <c r="C107" s="7">
+      <c r="C107" s="16">
         <v>368075</v>
       </c>
-      <c r="D107" s="8">
+      <c r="D107" s="17">
         <v>88</v>
       </c>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A108" s="10">
+    <row r="108">
+      <c r="A108" s="28">
         <v>43404</v>
       </c>
-      <c r="B108" s="7">
+      <c r="B108" s="16">
         <v>421586</v>
       </c>
-      <c r="C108" s="7">
+      <c r="C108" s="16">
         <v>368772</v>
       </c>
-      <c r="D108" s="8">
+      <c r="D108" s="17">
         <v>87.5</v>
       </c>
     </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A109" s="10">
+    <row r="109">
+      <c r="A109" s="28">
         <v>43434</v>
       </c>
-      <c r="B109" s="7">
+      <c r="B109" s="16">
         <v>423663</v>
       </c>
-      <c r="C109" s="7">
+      <c r="C109" s="16">
         <v>369835</v>
       </c>
-      <c r="D109" s="8">
+      <c r="D109" s="17">
         <v>87.3</v>
       </c>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A110" s="10">
+    <row r="110">
+      <c r="A110" s="28">
         <v>43465</v>
       </c>
-      <c r="B110" s="7">
+      <c r="B110" s="16">
         <v>426097</v>
       </c>
-      <c r="C110" s="7">
+      <c r="C110" s="16">
         <v>370815</v>
       </c>
-      <c r="D110" s="8">
+      <c r="D110" s="17">
         <v>87</v>
       </c>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A111" s="10">
+    <row r="111">
+      <c r="A111" s="28">
         <v>43496</v>
       </c>
-      <c r="B111" s="7">
+      <c r="B111" s="16">
         <v>427681</v>
       </c>
-      <c r="C111" s="7">
+      <c r="C111" s="16">
         <v>371861</v>
       </c>
-      <c r="D111" s="8">
+      <c r="D111" s="17">
         <v>86.9</v>
       </c>
     </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A112" s="10">
+    <row r="112">
+      <c r="A112" s="28">
         <v>43524</v>
       </c>
-      <c r="B112" s="7">
+      <c r="B112" s="16">
         <v>428782</v>
       </c>
-      <c r="C112" s="7">
+      <c r="C112" s="16">
         <v>373986</v>
       </c>
-      <c r="D112" s="8">
+      <c r="D112" s="17">
         <v>87.2</v>
       </c>
     </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A113" s="10">
+    <row r="113">
+      <c r="A113" s="28">
         <v>43555</v>
       </c>
-      <c r="B113" s="7">
+      <c r="B113" s="16">
         <v>430815</v>
       </c>
-      <c r="C113" s="7">
+      <c r="C113" s="16">
         <v>378284</v>
       </c>
-      <c r="D113" s="8">
+      <c r="D113" s="17">
         <v>87.8</v>
       </c>
     </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A114" s="10">
+    <row r="114">
+      <c r="A114" s="28">
         <v>43585</v>
       </c>
-      <c r="B114" s="7">
+      <c r="B114" s="16">
         <v>432414</v>
       </c>
-      <c r="C114" s="7">
+      <c r="C114" s="16">
         <v>380591</v>
       </c>
-      <c r="D114" s="8">
+      <c r="D114" s="17">
         <v>88</v>
       </c>
     </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A115" s="10">
+    <row r="115">
+      <c r="A115" s="28">
         <v>43616</v>
       </c>
-      <c r="B115" s="7">
+      <c r="B115" s="16">
         <v>435036</v>
       </c>
-      <c r="C115" s="7">
+      <c r="C115" s="16">
         <v>378870</v>
       </c>
-      <c r="D115" s="8">
+      <c r="D115" s="17">
         <v>87.1</v>
       </c>
     </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A116" s="10">
+    <row r="116">
+      <c r="A116" s="28">
         <v>43646</v>
       </c>
-      <c r="B116" s="7">
+      <c r="B116" s="16">
         <v>435788</v>
       </c>
-      <c r="C116" s="7">
+      <c r="C116" s="16">
         <v>380236</v>
       </c>
-      <c r="D116" s="8">
+      <c r="D116" s="17">
         <v>87.3</v>
       </c>
     </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A117" s="10">
+    <row r="117">
+      <c r="A117" s="28">
         <v>43677</v>
       </c>
-      <c r="B117" s="7">
+      <c r="B117" s="16">
         <v>438753</v>
       </c>
-      <c r="C117" s="7">
+      <c r="C117" s="16">
         <v>383803</v>
       </c>
-      <c r="D117" s="8">
+      <c r="D117" s="17">
         <v>87.5</v>
       </c>
     </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A118" s="10">
+    <row r="118">
+      <c r="A118" s="28">
         <v>43708</v>
       </c>
-      <c r="B118" s="7">
+      <c r="B118" s="16">
         <v>440899</v>
       </c>
-      <c r="C118" s="7">
+      <c r="C118" s="16">
         <v>381998</v>
       </c>
-      <c r="D118" s="8">
+      <c r="D118" s="17">
         <v>86.6</v>
       </c>
     </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A119" s="10">
+    <row r="119">
+      <c r="A119" s="28">
         <v>43738</v>
       </c>
-      <c r="B119" s="7">
+      <c r="B119" s="16">
         <v>443347</v>
       </c>
-      <c r="C119" s="7">
+      <c r="C119" s="16">
         <v>387308</v>
       </c>
-      <c r="D119" s="8">
+      <c r="D119" s="17">
         <v>87.4</v>
       </c>
     </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A120" s="10">
+    <row r="120">
+      <c r="A120" s="28">
         <v>43769</v>
       </c>
-      <c r="B120" s="7">
+      <c r="B120" s="16">
         <v>445613</v>
       </c>
-      <c r="C120" s="7">
+      <c r="C120" s="16">
         <v>388282</v>
       </c>
-      <c r="D120" s="8">
+      <c r="D120" s="17">
         <v>87.1</v>
       </c>
     </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A121" s="10">
+    <row r="121">
+      <c r="A121" s="28">
         <v>43799</v>
       </c>
-      <c r="B121" s="7">
+      <c r="B121" s="16">
         <v>446327</v>
       </c>
-      <c r="C121" s="7">
+      <c r="C121" s="16">
         <v>389615</v>
       </c>
-      <c r="D121" s="8">
+      <c r="D121" s="17">
         <v>87.3</v>
       </c>
     </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A122" s="10">
+    <row r="122">
+      <c r="A122" s="28">
         <v>43830</v>
       </c>
-      <c r="B122" s="7">
+      <c r="B122" s="16">
         <v>448572</v>
       </c>
-      <c r="C122" s="7">
+      <c r="C122" s="16">
         <v>389298</v>
       </c>
-      <c r="D122" s="8">
+      <c r="D122" s="17">
         <v>86.8</v>
       </c>
     </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A123" s="10">
+    <row r="123">
+      <c r="A123" s="28">
         <v>43861</v>
       </c>
-      <c r="B123" s="7">
+      <c r="B123" s="16">
         <v>450844</v>
       </c>
-      <c r="C123" s="7">
+      <c r="C123" s="16">
         <v>388303</v>
       </c>
-      <c r="D123" s="8">
+      <c r="D123" s="17">
         <v>86.1</v>
       </c>
     </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A124" s="10">
+    <row r="124">
+      <c r="A124" s="28">
         <v>43890</v>
       </c>
-      <c r="B124" s="7">
+      <c r="B124" s="16">
         <v>451619</v>
       </c>
-      <c r="C124" s="7">
+      <c r="C124" s="16">
         <v>393029</v>
       </c>
-      <c r="D124" s="8">
+      <c r="D124" s="17">
         <v>87</v>
       </c>
     </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A125" s="10">
+    <row r="125">
+      <c r="A125" s="28">
         <v>43921</v>
       </c>
-      <c r="B125" s="7">
+      <c r="B125" s="16">
         <v>454628</v>
       </c>
-      <c r="C125" s="7">
+      <c r="C125" s="16">
         <v>401277</v>
       </c>
-      <c r="D125" s="8">
+      <c r="D125" s="17">
         <v>88.3</v>
       </c>
     </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A126" s="10">
+    <row r="126">
+      <c r="A126" s="28">
         <v>43951</v>
       </c>
-      <c r="B126" s="7">
+      <c r="B126" s="16">
         <v>455563</v>
       </c>
-      <c r="C126" s="7">
+      <c r="C126" s="16">
         <v>404533</v>
       </c>
-      <c r="D126" s="8">
+      <c r="D126" s="17">
         <v>88.8</v>
       </c>
     </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A127" s="10">
+    <row r="127">
+      <c r="A127" s="28">
         <v>43982</v>
       </c>
-      <c r="B127" s="7">
+      <c r="B127" s="16">
         <v>456699</v>
       </c>
-      <c r="C127" s="7">
+      <c r="C127" s="16">
         <v>403477</v>
       </c>
-      <c r="D127" s="8">
+      <c r="D127" s="17">
         <v>88.3</v>
       </c>
     </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A128" s="10">
+    <row r="128">
+      <c r="A128" s="28">
         <v>44012</v>
       </c>
-      <c r="B128" s="7">
+      <c r="B128" s="16">
         <v>454642</v>
       </c>
-      <c r="C128" s="7">
+      <c r="C128" s="16">
         <v>401393</v>
       </c>
-      <c r="D128" s="8">
+      <c r="D128" s="17">
         <v>88.3</v>
       </c>
     </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A129" s="10">
+    <row r="129">
+      <c r="A129" s="28">
         <v>44043</v>
       </c>
-      <c r="B129" s="7">
+      <c r="B129" s="16">
         <v>455395</v>
       </c>
-      <c r="C129" s="7">
+      <c r="C129" s="16">
         <v>402860</v>
       </c>
-      <c r="D129" s="8">
+      <c r="D129" s="17">
         <v>88.5</v>
       </c>
     </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A130" s="10">
+    <row r="130">
+      <c r="A130" s="28">
         <v>44074</v>
       </c>
-      <c r="B130" s="7">
+      <c r="B130" s="16">
         <v>455440</v>
       </c>
-      <c r="C130" s="7">
+      <c r="C130" s="16">
         <v>403738</v>
       </c>
-      <c r="D130" s="8">
+      <c r="D130" s="17">
         <v>88.6</v>
       </c>
     </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A131" s="10">
+    <row r="131">
+      <c r="A131" s="28">
         <v>44104</v>
       </c>
-      <c r="B131" s="7">
+      <c r="B131" s="16">
         <v>456356</v>
       </c>
-      <c r="C131" s="7">
+      <c r="C131" s="16">
         <v>404489</v>
       </c>
-      <c r="D131" s="8">
+      <c r="D131" s="17">
         <v>88.6</v>
       </c>
     </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A132" s="10">
+    <row r="132">
+      <c r="A132" s="28">
         <v>44135</v>
       </c>
-      <c r="B132" s="7">
+      <c r="B132" s="16">
         <v>459743</v>
       </c>
-      <c r="C132" s="7">
+      <c r="C132" s="16">
         <v>406109</v>
       </c>
-      <c r="D132" s="8">
+      <c r="D132" s="17">
         <v>88.3</v>
       </c>
     </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A133" s="10">
+    <row r="133">
+      <c r="A133" s="28">
         <v>44165</v>
       </c>
-      <c r="B133" s="7">
+      <c r="B133" s="16">
         <v>456962</v>
       </c>
-      <c r="C133" s="7">
+      <c r="C133" s="16">
         <v>404304</v>
       </c>
-      <c r="D133" s="8">
+      <c r="D133" s="17">
         <v>88.5</v>
       </c>
     </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A134" s="10">
+    <row r="134">
+      <c r="A134" s="28">
         <v>44196</v>
       </c>
-      <c r="B134" s="7">
+      <c r="B134" s="16">
         <v>459512</v>
       </c>
-      <c r="C134" s="7">
+      <c r="C134" s="16">
         <v>407593</v>
       </c>
-      <c r="D134" s="8">
+      <c r="D134" s="17">
         <v>88.7</v>
       </c>
     </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A135" s="10">
+    <row r="135">
+      <c r="A135" s="28">
         <v>44227</v>
       </c>
-      <c r="B135" s="7">
+      <c r="B135" s="16">
         <v>462233</v>
       </c>
-      <c r="C135" s="7">
+      <c r="C135" s="16">
         <v>402677</v>
       </c>
-      <c r="D135" s="8">
+      <c r="D135" s="17">
         <v>87.1</v>
       </c>
     </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A136" s="10">
+    <row r="136">
+      <c r="A136" s="28">
         <v>44255</v>
       </c>
-      <c r="B136" s="7">
+      <c r="B136" s="16">
         <v>465398</v>
       </c>
-      <c r="C136" s="7">
+      <c r="C136" s="16">
         <v>402542</v>
       </c>
-      <c r="D136" s="8">
+      <c r="D136" s="17">
         <v>86.5</v>
       </c>
     </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A137" s="10">
+    <row r="137">
+      <c r="A137" s="28">
         <v>44286</v>
       </c>
-      <c r="B137" s="7">
+      <c r="B137" s="16">
         <v>468569</v>
       </c>
-      <c r="C137" s="7">
+      <c r="C137" s="16">
         <v>406783</v>
       </c>
-      <c r="D137" s="8">
+      <c r="D137" s="17">
         <v>86.8</v>
       </c>
     </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A138" s="10">
+    <row r="138">
+      <c r="A138" s="28">
         <v>44316</v>
       </c>
-      <c r="B138" s="7">
+      <c r="B138" s="16">
         <v>470448</v>
       </c>
-      <c r="C138" s="7">
+      <c r="C138" s="16">
         <v>406940</v>
       </c>
-      <c r="D138" s="8">
+      <c r="D138" s="17">
         <v>86.5</v>
       </c>
     </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A139" s="10">
+    <row r="139">
+      <c r="A139" s="28">
         <v>44347</v>
       </c>
-      <c r="B139" s="7">
+      <c r="B139" s="16">
         <v>474383</v>
       </c>
-      <c r="C139" s="7">
+      <c r="C139" s="16">
         <v>406378</v>
       </c>
-      <c r="D139" s="8">
+      <c r="D139" s="17">
         <v>85.7</v>
       </c>
     </row>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A140" s="10">
+    <row r="140">
+      <c r="A140" s="28">
         <v>44377</v>
       </c>
-      <c r="B140" s="7">
+      <c r="B140" s="16">
         <v>477980</v>
       </c>
-      <c r="C140" s="7">
+      <c r="C140" s="16">
         <v>413933</v>
       </c>
-      <c r="D140" s="8">
+      <c r="D140" s="17">
         <v>86.6</v>
       </c>
     </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A141" s="10">
+    <row r="141">
+      <c r="A141" s="28">
         <v>44408</v>
       </c>
-      <c r="B141" s="7">
+      <c r="B141" s="16">
         <v>481470</v>
       </c>
-      <c r="C141" s="7">
+      <c r="C141" s="16">
         <v>419246</v>
       </c>
-      <c r="D141" s="8">
+      <c r="D141" s="17">
         <v>87.1</v>
       </c>
     </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A142" s="10">
+    <row r="142">
+      <c r="A142" s="28">
         <v>44439</v>
       </c>
-      <c r="B142" s="7">
+      <c r="B142" s="16">
         <v>484714</v>
       </c>
-      <c r="C142" s="7">
+      <c r="C142" s="16">
         <v>418282</v>
       </c>
-      <c r="D142" s="8">
+      <c r="D142" s="17">
         <v>86.3</v>
       </c>
     </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A143" s="10">
+    <row r="143">
+      <c r="A143" s="28">
         <v>44469</v>
       </c>
-      <c r="B143" s="7">
+      <c r="B143" s="16">
         <v>488040</v>
       </c>
-      <c r="C143" s="7">
+      <c r="C143" s="16">
         <v>426214</v>
       </c>
-      <c r="D143" s="8">
+      <c r="D143" s="17">
         <v>87.3</v>
       </c>
     </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A144" s="10">
+    <row r="144">
+      <c r="A144" s="28">
         <v>44500</v>
       </c>
-      <c r="B144" s="7">
+      <c r="B144" s="16">
         <v>488840</v>
       </c>
-      <c r="C144" s="7">
+      <c r="C144" s="16">
         <v>429157</v>
       </c>
-      <c r="D144" s="8">
+      <c r="D144" s="17">
         <v>87.8</v>
       </c>
     </row>
-    <row r="145" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A145" s="10">
+    <row r="145">
+      <c r="A145" s="28">
         <v>44530</v>
       </c>
-      <c r="B145" s="7">
+      <c r="B145" s="16">
         <v>490763</v>
       </c>
-      <c r="C145" s="7">
+      <c r="C145" s="16">
         <v>431554</v>
       </c>
-      <c r="D145" s="8">
+      <c r="D145" s="17">
         <v>87.9</v>
       </c>
     </row>
-    <row r="146" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A146" s="10">
+    <row r="146">
+      <c r="A146" s="28">
         <v>44561</v>
       </c>
-      <c r="B146" s="7">
+      <c r="B146" s="16">
         <v>493159</v>
       </c>
-      <c r="C146" s="7">
+      <c r="C146" s="16">
         <v>439305</v>
       </c>
-      <c r="D146" s="8">
+      <c r="D146" s="17">
         <v>89.1</v>
       </c>
     </row>
-    <row r="147" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A147" s="10">
+    <row r="147">
+      <c r="A147" s="28">
         <v>44592</v>
       </c>
-      <c r="B147" s="7">
+      <c r="B147" s="16">
         <v>496893</v>
       </c>
-      <c r="C147" s="7">
+      <c r="C147" s="16">
         <v>440023</v>
       </c>
-      <c r="D147" s="8">
+      <c r="D147" s="17">
         <v>88.6</v>
       </c>
     </row>
-    <row r="148" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A148" s="10">
+    <row r="148">
+      <c r="A148" s="28">
         <v>44620</v>
       </c>
-      <c r="B148" s="7">
+      <c r="B148" s="16">
         <v>499047</v>
       </c>
-      <c r="C148" s="7">
+      <c r="C148" s="16">
         <v>443243</v>
       </c>
-      <c r="D148" s="8">
+      <c r="D148" s="17">
         <v>88.8</v>
       </c>
     </row>
-    <row r="149" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A149" s="10">
+    <row r="149">
+      <c r="A149" s="28">
         <v>44651</v>
       </c>
-      <c r="B149" s="7">
+      <c r="B149" s="16">
         <v>501788</v>
       </c>
-      <c r="C149" s="7">
+      <c r="C149" s="16">
         <v>449321</v>
       </c>
-      <c r="D149" s="8">
+      <c r="D149" s="17">
         <v>89.5</v>
       </c>
     </row>
-    <row r="150" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A150" s="10">
+    <row r="150">
+      <c r="A150" s="28">
         <v>44681</v>
       </c>
-      <c r="B150" s="7">
+      <c r="B150" s="16">
         <v>503502</v>
       </c>
-      <c r="C150" s="7">
+      <c r="C150" s="16">
         <v>451121</v>
       </c>
-      <c r="D150" s="8">
+      <c r="D150" s="17">
         <v>89.6</v>
       </c>
     </row>
-    <row r="151" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A151" s="10">
+    <row r="151">
+      <c r="A151" s="28">
         <v>44712</v>
       </c>
-      <c r="B151" s="7">
+      <c r="B151" s="16">
         <v>505035</v>
       </c>
-      <c r="C151" s="7">
+      <c r="C151" s="16">
         <v>449127</v>
       </c>
-      <c r="D151" s="8">
+      <c r="D151" s="17">
         <v>88.9</v>
       </c>
     </row>
-    <row r="152" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A152" s="10">
+    <row r="152">
+      <c r="A152" s="28">
         <v>44742</v>
       </c>
-      <c r="B152" s="7">
+      <c r="B152" s="16">
         <v>507023</v>
       </c>
-      <c r="C152" s="7">
+      <c r="C152" s="16">
         <v>455898</v>
       </c>
-      <c r="D152" s="8">
+      <c r="D152" s="17">
         <v>89.9</v>
       </c>
     </row>
-    <row r="153" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A153" s="10">
+    <row r="153">
+      <c r="A153" s="28">
         <v>44773</v>
       </c>
-      <c r="B153" s="7">
+      <c r="B153" s="16">
         <v>509100</v>
       </c>
-      <c r="C153" s="7">
+      <c r="C153" s="16">
         <v>458777</v>
       </c>
-      <c r="D153" s="8">
+      <c r="D153" s="17">
         <v>90.1</v>
       </c>
     </row>
-    <row r="154" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A154" s="10">
+    <row r="154">
+      <c r="A154" s="28">
         <v>44804</v>
       </c>
-      <c r="B154" s="7">
+      <c r="B154" s="16">
         <v>510979</v>
       </c>
-      <c r="C154" s="7">
+      <c r="C154" s="16">
         <v>460190</v>
       </c>
-      <c r="D154" s="8">
+      <c r="D154" s="17">
         <v>90.1</v>
       </c>
     </row>
-    <row r="155" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A155" s="10">
+    <row r="155">
+      <c r="A155" s="28">
         <v>44834</v>
       </c>
-      <c r="B155" s="7">
+      <c r="B155" s="16">
         <v>512495</v>
       </c>
-      <c r="C155" s="7">
+      <c r="C155" s="16">
         <v>464139</v>
       </c>
-      <c r="D155" s="8">
+      <c r="D155" s="17">
         <v>90.6</v>
       </c>
     </row>
-    <row r="156" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A156" s="10">
+    <row r="156">
+      <c r="A156" s="28">
         <v>44865</v>
       </c>
-      <c r="B156" s="7">
+      <c r="B156" s="16">
         <v>513950</v>
       </c>
-      <c r="C156" s="7">
+      <c r="C156" s="16">
         <v>464701</v>
       </c>
-      <c r="D156" s="8">
+      <c r="D156" s="17">
         <v>90.4</v>
       </c>
     </row>
-    <row r="157" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A157" s="10">
+    <row r="157">
+      <c r="A157" s="28">
         <v>44895</v>
       </c>
-      <c r="B157" s="7">
+      <c r="B157" s="16">
         <v>514844</v>
       </c>
-      <c r="C157" s="7">
+      <c r="C157" s="16">
         <v>468681</v>
       </c>
-      <c r="D157" s="8">
+      <c r="D157" s="17">
         <v>91</v>
       </c>
     </row>
-    <row r="158" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A158" s="10">
+    <row r="158">
+      <c r="A158" s="28">
         <v>44926</v>
       </c>
-      <c r="B158" s="7">
+      <c r="B158" s="16">
         <v>515978</v>
       </c>
-      <c r="C158" s="7">
+      <c r="C158" s="16">
         <v>470526</v>
       </c>
-      <c r="D158" s="8">
+      <c r="D158" s="17">
         <v>91.2</v>
       </c>
     </row>
-    <row r="159" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A159" s="10">
+    <row r="159">
+      <c r="A159" s="28">
         <v>44957</v>
       </c>
-      <c r="B159" s="7">
+      <c r="B159" s="16">
         <v>518850</v>
       </c>
-      <c r="C159" s="7">
+      <c r="C159" s="16">
         <v>465000</v>
       </c>
-      <c r="D159" s="8">
+      <c r="D159" s="17">
         <v>89.6</v>
       </c>
     </row>
-    <row r="160" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A160" s="10">
+    <row r="160">
+      <c r="A160" s="28">
         <v>44985</v>
       </c>
-      <c r="B160" s="7">
+      <c r="B160" s="16">
         <v>518548</v>
       </c>
-      <c r="C160" s="7">
+      <c r="C160" s="16">
         <v>469177</v>
       </c>
-      <c r="D160" s="8">
+      <c r="D160" s="17">
         <v>90.5</v>
       </c>
     </row>
-    <row r="161" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A161" s="10">
+    <row r="161">
+      <c r="A161" s="28">
         <v>45016</v>
       </c>
-      <c r="B161" s="7">
+      <c r="B161" s="16">
         <v>520256</v>
       </c>
-      <c r="C161" s="7">
+      <c r="C161" s="16">
         <v>470083</v>
       </c>
-      <c r="D161" s="8">
+      <c r="D161" s="17">
         <v>90.4</v>
       </c>
     </row>
-    <row r="162" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A162" s="10">
+    <row r="162">
+      <c r="A162" s="28">
         <v>45046</v>
       </c>
-      <c r="B162" s="7">
+      <c r="B162" s="16">
         <v>521504</v>
       </c>
-      <c r="C162" s="7">
+      <c r="C162" s="16">
         <v>470507</v>
       </c>
-      <c r="D162" s="8">
+      <c r="D162" s="17">
         <v>90.2</v>
       </c>
     </row>
-    <row r="163" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A163" s="10">
+    <row r="163">
+      <c r="A163" s="28">
         <v>45077</v>
       </c>
-      <c r="B163" s="7">
+      <c r="B163" s="16">
         <v>521878</v>
       </c>
-      <c r="C163" s="7">
+      <c r="C163" s="16">
         <v>468163</v>
       </c>
-      <c r="D163" s="8">
+      <c r="D163" s="17">
         <v>89.7</v>
       </c>
     </row>
-    <row r="164" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A164" s="10">
+    <row r="164">
+      <c r="A164" s="28">
         <v>45107</v>
       </c>
-      <c r="B164" s="7">
+      <c r="B164" s="16">
         <v>522438</v>
       </c>
-      <c r="C164" s="7">
+      <c r="C164" s="16">
         <v>471799</v>
       </c>
-      <c r="D164" s="8">
+      <c r="D164" s="17">
         <v>90.3</v>
       </c>
     </row>
-    <row r="165" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A165" s="10">
+    <row r="165">
+      <c r="A165" s="28">
         <v>45138</v>
       </c>
-      <c r="B165" s="7">
+      <c r="B165" s="16">
         <v>523709</v>
       </c>
-      <c r="C165" s="7">
+      <c r="C165" s="16">
         <v>475219</v>
       </c>
-      <c r="D165" s="8">
+      <c r="D165" s="17">
         <v>90.7</v>
       </c>
     </row>
-    <row r="166" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A166" s="10">
+    <row r="166">
+      <c r="A166" s="28">
         <v>45169</v>
       </c>
-      <c r="B166" s="7">
+      <c r="B166" s="16">
         <v>526027</v>
       </c>
-      <c r="C166" s="7">
+      <c r="C166" s="16">
         <v>475816</v>
       </c>
-      <c r="D166" s="8">
+      <c r="D166" s="17">
         <v>90.5</v>
       </c>
     </row>
-    <row r="167" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A167" s="10">
+    <row r="167">
+      <c r="A167" s="28">
         <v>45199</v>
       </c>
-      <c r="B167" s="7">
+      <c r="B167" s="16">
         <v>526564</v>
       </c>
-      <c r="C167" s="7">
+      <c r="C167" s="16">
         <v>475624</v>
       </c>
-      <c r="D167" s="8">
+      <c r="D167" s="17">
         <v>90.3</v>
       </c>
     </row>
-    <row r="168" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A168" s="10">
+    <row r="168">
+      <c r="A168" s="28">
         <v>45230</v>
       </c>
-      <c r="B168" s="7">
+      <c r="B168" s="16">
         <v>527374</v>
       </c>
-      <c r="C168" s="7">
+      <c r="C168" s="16">
         <v>476884</v>
       </c>
-      <c r="D168" s="8">
+      <c r="D168" s="17">
         <v>90.4</v>
       </c>
     </row>
-    <row r="169" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A169" s="10">
+    <row r="169">
+      <c r="A169" s="28">
         <v>45260</v>
       </c>
-      <c r="B169" s="7">
+      <c r="B169" s="16">
         <v>528588</v>
       </c>
-      <c r="C169" s="7">
+      <c r="C169" s="16">
         <v>479052</v>
       </c>
-      <c r="D169" s="8">
+      <c r="D169" s="17">
         <v>90.6</v>
       </c>
     </row>
-    <row r="170" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A170" s="10">
+    <row r="170">
+      <c r="A170" s="28">
         <v>45291</v>
       </c>
-      <c r="B170" s="7">
+      <c r="B170" s="16">
         <v>530186</v>
       </c>
-      <c r="C170" s="7">
+      <c r="C170" s="16">
         <v>481816</v>
       </c>
-      <c r="D170" s="8">
+      <c r="D170" s="17">
         <v>90.9</v>
       </c>
     </row>
-    <row r="171" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A171" s="10">
+    <row r="171">
+      <c r="A171" s="28">
         <v>45322</v>
       </c>
-      <c r="B171" s="7">
+      <c r="B171" s="16">
         <v>532411</v>
       </c>
-      <c r="C171" s="7">
+      <c r="C171" s="16">
         <v>479587</v>
       </c>
-      <c r="D171" s="8">
+      <c r="D171" s="17">
         <v>90.1</v>
       </c>
     </row>
-    <row r="172" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A172" s="10">
+    <row r="172">
+      <c r="A172" s="28">
         <v>45351</v>
       </c>
-      <c r="B172" s="7">
+      <c r="B172" s="16">
         <v>533030</v>
       </c>
-      <c r="C172" s="7">
+      <c r="C172" s="16">
         <v>478005</v>
       </c>
-      <c r="D172" s="8">
+      <c r="D172" s="17">
         <v>89.7</v>
       </c>
     </row>
-    <row r="173" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A173" s="10">
+    <row r="173">
+      <c r="A173" s="28">
         <v>45382</v>
       </c>
-      <c r="B173" s="7">
+      <c r="B173" s="16">
         <v>534406</v>
       </c>
-      <c r="C173" s="7">
+      <c r="C173" s="16">
         <v>479336</v>
       </c>
-      <c r="D173" s="8">
+      <c r="D173" s="17">
         <v>89.7</v>
       </c>
     </row>
-    <row r="174" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A174" s="10">
+    <row r="174">
+      <c r="A174" s="28">
         <v>45412</v>
       </c>
-      <c r="B174" s="7">
+      <c r="B174" s="16">
         <v>535787</v>
       </c>
-      <c r="C174" s="7">
+      <c r="C174" s="16">
         <v>480069</v>
       </c>
-      <c r="D174" s="8">
+      <c r="D174" s="17">
         <v>89.6</v>
       </c>
     </row>
-    <row r="175" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A175" s="10">
+    <row r="175">
+      <c r="A175" s="28">
         <v>45443</v>
       </c>
-      <c r="B175" s="7">
+      <c r="B175" s="16">
         <v>536713</v>
       </c>
-      <c r="C175" s="7">
+      <c r="C175" s="16">
         <v>478485</v>
       </c>
-      <c r="D175" s="8">
+      <c r="D175" s="17">
         <v>89.2</v>
       </c>
     </row>
-    <row r="176" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A176" s="10">
+    <row r="176">
+      <c r="A176" s="28">
         <v>45473</v>
       </c>
-      <c r="B176" s="7">
+      <c r="B176" s="16">
         <v>536924</v>
       </c>
-      <c r="C176" s="7">
+      <c r="C176" s="16">
         <v>478146</v>
       </c>
-      <c r="D176" s="8">
+      <c r="D176" s="17">
         <v>89.1</v>
       </c>
     </row>
-    <row r="177" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A177" s="10">
+    <row r="177">
+      <c r="A177" s="28">
         <v>45504</v>
       </c>
-      <c r="B177" s="7">
+      <c r="B177" s="16">
         <v>539681</v>
       </c>
-      <c r="C177" s="7">
+      <c r="C177" s="16">
         <v>482177</v>
       </c>
-      <c r="D177" s="8">
+      <c r="D177" s="17">
         <v>89.3</v>
       </c>
     </row>
-    <row r="178" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A178" s="10">
+    <row r="178">
+      <c r="A178" s="28">
         <v>45535</v>
       </c>
-      <c r="B178" s="7">
+      <c r="B178" s="16">
         <v>541411</v>
       </c>
-      <c r="C178" s="7">
+      <c r="C178" s="16">
         <v>478334</v>
       </c>
-      <c r="D178" s="8">
+      <c r="D178" s="17">
         <v>88.3</v>
       </c>
     </row>
-    <row r="179" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A179" s="10">
+    <row r="179">
+      <c r="A179" s="28">
         <v>45565</v>
       </c>
-      <c r="B179" s="7">
+      <c r="B179" s="16">
         <v>541912</v>
       </c>
-      <c r="C179" s="7">
+      <c r="C179" s="16">
         <v>479532</v>
       </c>
-      <c r="D179" s="8">
+      <c r="D179" s="17">
         <v>88.5</v>
       </c>
     </row>
-    <row r="180" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A180" s="10">
+    <row r="180">
+      <c r="A180" s="28">
         <v>45596</v>
       </c>
-      <c r="B180" s="7">
+      <c r="B180" s="16">
         <v>544573</v>
       </c>
-      <c r="C180" s="7">
+      <c r="C180" s="16">
         <v>484103</v>
       </c>
-      <c r="D180" s="8">
+      <c r="D180" s="17">
         <v>88.9</v>
       </c>
     </row>
-    <row r="181" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A181" s="10">
+    <row r="181">
+      <c r="A181" s="28">
         <v>45626</v>
       </c>
-      <c r="B181" s="7">
+      <c r="B181" s="16">
         <v>545747</v>
       </c>
-      <c r="C181" s="7">
+      <c r="C181" s="16">
         <v>486455</v>
       </c>
-      <c r="D181" s="8">
+      <c r="D181" s="17">
         <v>89.1</v>
       </c>
     </row>
-    <row r="182" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A182" s="10">
+    <row r="182">
+      <c r="A182" s="28">
         <v>45657</v>
       </c>
-      <c r="B182" s="7">
+      <c r="B182" s="16">
         <v>546794</v>
       </c>
-      <c r="C182" s="7">
+      <c r="C182" s="16">
         <v>492601</v>
       </c>
-      <c r="D182" s="8">
+      <c r="D182" s="17">
         <v>90.1</v>
       </c>
     </row>
-    <row r="183" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A183" s="10">
+    <row r="183">
+      <c r="A183" s="28">
         <v>45688</v>
       </c>
-      <c r="B183" s="7">
+      <c r="B183" s="16">
         <v>549310</v>
       </c>
-      <c r="C183" s="7">
+      <c r="C183" s="16">
         <v>489997</v>
       </c>
-      <c r="D183" s="8">
+      <c r="D183" s="17">
         <v>89.2</v>
       </c>
     </row>
-    <row r="184" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A184" s="10">
+    <row r="184">
+      <c r="A184" s="28">
         <v>45716</v>
       </c>
-      <c r="B184" s="7">
+      <c r="B184" s="16">
         <v>550649</v>
       </c>
-      <c r="C184" s="7">
+      <c r="C184" s="16">
         <v>491785</v>
       </c>
-      <c r="D184" s="8">
+      <c r="D184" s="17">
         <v>89.3</v>
       </c>
     </row>
-    <row r="185" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A185" s="10">
+    <row r="185">
+      <c r="A185" s="28">
         <v>45747</v>
       </c>
-      <c r="B185" s="7">
+      <c r="B185" s="16">
         <v>552304</v>
       </c>
-      <c r="C185" s="7">
+      <c r="C185" s="16">
         <v>494546</v>
       </c>
-      <c r="D185" s="8">
+      <c r="D185" s="17">
         <v>89.5</v>
       </c>
     </row>
-    <row r="186" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A186" s="10">
+    <row r="186">
+      <c r="A186" s="28">
         <v>45777</v>
       </c>
-      <c r="B186" s="7">
+      <c r="B186" s="16">
         <v>553132</v>
       </c>
-      <c r="C186" s="7">
+      <c r="C186" s="16">
         <v>496765</v>
       </c>
-      <c r="D186" s="8">
+      <c r="D186" s="17">
         <v>89.8</v>
       </c>
     </row>
-    <row r="187" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A187" s="10">
+    <row r="187">
+      <c r="A187" s="28">
         <v>45808</v>
       </c>
-      <c r="B187" s="7">
+      <c r="B187" s="16">
         <v>554797</v>
       </c>
-      <c r="C187" s="7">
+      <c r="C187" s="16">
         <v>494593</v>
       </c>
-      <c r="D187" s="8">
+      <c r="D187" s="17">
         <v>89.1</v>
       </c>
     </row>
-    <row r="188" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A188" s="10">
+    <row r="188">
+      <c r="A188" s="28">
         <v>45838</v>
       </c>
-      <c r="B188" s="7">
+      <c r="B188" s="16">
         <v>555797</v>
       </c>
-      <c r="C188" s="7">
+      <c r="C188" s="16">
         <v>496644</v>
       </c>
-      <c r="D188" s="8">
+      <c r="D188" s="17">
         <v>89.4</v>
       </c>
     </row>
-    <row r="189" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A189" s="10">
+    <row r="189">
+      <c r="A189" s="28">
         <v>45869</v>
       </c>
-      <c r="B189" s="7">
+      <c r="B189" s="16">
         <v>559598</v>
       </c>
-      <c r="C189" s="7">
+      <c r="C189" s="16">
         <v>502146</v>
       </c>
-      <c r="D189" s="8">
+      <c r="D189" s="17">
         <v>89.7</v>
       </c>
     </row>
-    <row r="190" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A190" s="10">
+    <row r="190">
+      <c r="A190" s="28">
         <v>45900</v>
       </c>
-      <c r="B190" s="7">
+      <c r="B190" s="16">
         <v>562690</v>
       </c>
-      <c r="C190" s="7">
+      <c r="C190" s="16">
         <v>499828</v>
       </c>
-      <c r="D190" s="8">
+      <c r="D190" s="17">
         <v>88.8</v>
       </c>
     </row>
-    <row r="191" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A191" s="10">
+    <row r="191">
+      <c r="A191" s="28">
         <v>45930</v>
       </c>
-      <c r="B191" s="7">
+      <c r="B191" s="16">
         <v>564203</v>
       </c>
-      <c r="C191" s="7">
+      <c r="C191" s="16">
         <v>505068</v>
       </c>
-      <c r="D191" s="8">
+      <c r="D191" s="17">
         <v>89.5</v>
       </c>
     </row>
-    <row r="192" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A192" s="10">
+    <row r="192">
+      <c r="A192" s="28">
         <v>45961</v>
       </c>
-      <c r="B192" s="7">
+      <c r="B192" s="16">
         <v>567931</v>
       </c>
-      <c r="C192" s="7">
+      <c r="C192" s="16">
         <v>509979</v>
       </c>
-      <c r="D192" s="8">
+      <c r="D192" s="17">
         <v>89.8</v>
       </c>
     </row>
-    <row r="193" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A193" s="10">
+    <row r="193">
+      <c r="A193" s="28">
         <v>45991</v>
       </c>
-      <c r="B193" s="7">
+      <c r="B193" s="16">
         <v>570688</v>
       </c>
-      <c r="C193" s="7">
+      <c r="C193" s="16">
         <v>510823</v>
       </c>
-      <c r="D193" s="8">
+      <c r="D193" s="17">
         <v>89.5</v>
       </c>
     </row>
-    <row r="194" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A194" s="10">
+    <row r="194">
+      <c r="A194" s="28">
         <v>46022</v>
       </c>
-      <c r="B194" s="7">
+      <c r="B194" s="16">
         <v>573826</v>
       </c>
-      <c r="C194" s="7">
+      <c r="C194" s="16">
         <v>515031</v>
       </c>
-      <c r="D194" s="8">
+      <c r="D194" s="17">
         <v>89.8</v>
       </c>
     </row>
-    <row r="195" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A195" s="10">
+    <row r="195">
+      <c r="A195" s="28">
         <v>46053</v>
       </c>
-      <c r="B195" s="7">
+      <c r="B195" s="16">
         <v>575626</v>
       </c>
-      <c r="C195" s="7">
+      <c r="C195" s="16">
         <v>513776</v>
       </c>
-      <c r="D195" s="8">
+      <c r="D195" s="17">
         <v>89.3</v>
       </c>
     </row>
-    <row r="196" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A196" s="10">
+    <row r="196">
+      <c r="A196" s="28">
         <v>46081</v>
       </c>
-      <c r="B196" s="7">
+      <c r="B196" s="16">
         <v>578332</v>
       </c>
-      <c r="C196" s="7">
+      <c r="C196" s="16">
         <v>515716</v>
       </c>
-      <c r="D196" s="8">
+      <c r="D196" s="17">
         <v>89.2</v>
       </c>
     </row>
-    <row r="197" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A197" s="10">
+    <row r="197">
+      <c r="A197" s="28">
         <v>46112</v>
       </c>
-      <c r="B197" s="7">
+      <c r="B197" s="16">
         <v>580806</v>
       </c>
-      <c r="C197" s="7">
+      <c r="C197" s="16">
         <v>519655</v>
       </c>
-      <c r="D197" s="8">
+      <c r="D197" s="17">
         <v>89.5</v>
       </c>
     </row>
-    <row r="198" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A198" s="10">
+    <row r="198">
+      <c r="A198" s="28">
         <v>46142</v>
       </c>
-      <c r="B198" s="7">
+      <c r="B198" s="16">
         <v>581863</v>
       </c>
-      <c r="C198" s="7">
+      <c r="C198" s="16">
         <v>524248</v>
       </c>
-      <c r="D198" s="8">
+      <c r="D198" s="17">
         <v>90.1</v>
       </c>
     </row>
-    <row r="199" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A199" s="10">
+    <row r="199">
+      <c r="A199" s="28">
         <v>46173</v>
       </c>
-      <c r="B199" s="7">
+      <c r="B199" s="16">
         <v>585452</v>
       </c>
-      <c r="C199" s="7">
+      <c r="C199" s="16">
         <v>522566</v>
       </c>
-      <c r="D199" s="8">
+      <c r="D199" s="17">
         <v>89.3</v>
       </c>
     </row>
-    <row r="200" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A200" s="10">
+    <row r="200">
+      <c r="A200" s="28">
         <v>46203</v>
       </c>
-      <c r="B200" s="7">
+      <c r="B200" s="16">
         <v>585467</v>
       </c>
-      <c r="C200" s="7">
+      <c r="C200" s="16">
         <v>524898</v>
       </c>
-      <c r="D200" s="8">
+      <c r="D200" s="17">
         <v>89.7</v>
       </c>
     </row>
-    <row r="201" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A201" s="10">
+    <row r="201">
+      <c r="A201" s="28">
         <v>46234</v>
       </c>
-      <c r="B201" s="7">
+      <c r="B201" s="16">
         <v>588845</v>
       </c>
-      <c r="C201" s="7">
+      <c r="C201" s="16">
         <v>525269</v>
       </c>
-      <c r="D201" s="8">
+      <c r="D201" s="17">
         <v>89.2</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="28">
+        <v>46265</v>
+      </c>
+      <c r="B202" s="16">
+        <v>592198</v>
+      </c>
+      <c r="C202" s="16">
+        <v>522249</v>
+      </c>
+      <c r="D202" s="17">
+        <v>88.2</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B5" location="'Series Definitions'!R2C3" display="LIQ.MBA8" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="C5" location="'Series Definitions'!R3C3" display="LIQ.MBA5.ZZZZZR4" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="D5" location="'Series Definitions'!R4C3" display="LIQ.MBA7.ZZZZZR4" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="B5" location="'Series Definitions'!R2C3"/>
+    <hyperlink ref="C5" location="'Series Definitions'!R3C3"/>
+    <hyperlink ref="D5" location="'Series Definitions'!R4C3"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter>
-    <oddHeader>&amp;C&amp;"Aptos"&amp;10&amp;K000000 UNCLASSIFIED&amp;1#_x000D_</oddHeader>
-    <oddFooter>&amp;C_x000D_&amp;1#&amp;"Aptos"&amp;10&amp;K000000 UNCLASSIFIED</oddFooter>
-  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:B9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="19.5703125" customWidth="1" collapsed="1"/>
-    <col min="2" max="2" width="78.140625" customWidth="1" collapsed="1"/>
+    <col min="1" max="1" width="19.53125" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" width="78.125" customWidth="1" collapsed="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="7" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2">
       <c r="A2" s="3" t="s">
         <v>15</v>
       </c>
@@ -3419,7 +3256,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3">
       <c r="A3" s="3" t="s">
         <v>17</v>
       </c>
@@ -3427,20 +3264,21 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4">
       <c r="A4" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="9">
-        <v>46268</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B4" s="27">
+        <v>46296</v>
+      </c>
+    </row>
+    <row r="5"/>
+    <row r="6">
       <c r="A6" s="3" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7">
       <c r="A7" s="3">
         <v>1</v>
       </c>
@@ -3448,7 +3286,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8">
       <c r="A8" s="3">
         <v>2</v>
       </c>
@@ -3456,7 +3294,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="9">
       <c r="A9" s="3">
         <v>3</v>
       </c>
@@ -3466,28 +3304,25 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B1" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
+    <hyperlink ref="B1" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter>
-    <oddHeader>&amp;C&amp;"Aptos"&amp;10&amp;K000000 UNCLASSIFIED&amp;1#_x000D_</oddHeader>
-    <oddFooter>&amp;C_x000D_&amp;1#&amp;"Aptos"&amp;10&amp;K000000 UNCLASSIFIED</oddFooter>
-  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="2" width="46.85546875" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="20.5703125" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="19.5703125" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="78.140625" customWidth="1" collapsed="1"/>
+    <col min="1" max="1" width="46.875" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" width="46.875" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="20.5078125" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="19.53125" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="78.125" customWidth="1" collapsed="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" s="4" t="s">
         <v>23</v>
       </c>
@@ -3504,14 +3339,14 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="51" x14ac:dyDescent="0.25">
+    <row r="2">
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="C2" s="32" t="s">
         <v>4</v>
       </c>
       <c r="D2" s="3" t="s">
@@ -3521,28 +3356,28 @@
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3">
       <c r="A3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="32" t="s">
         <v>6</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4">
       <c r="A4" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="32" t="s">
         <v>9</v>
       </c>
       <c r="D4" s="3" t="s">
@@ -3551,14 +3386,10 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C2" location="'Data'!R5C2" display="LIQ.MBA8" xr:uid="{00000000-0004-0000-0200-000000000000}"/>
-    <hyperlink ref="C3" location="'Data'!R5C3" display="LIQ.MBA5.ZZZZZR4" xr:uid="{00000000-0004-0000-0200-000001000000}"/>
-    <hyperlink ref="C4" location="'Data'!R5C4" display="LIQ.MBA7.ZZZZZR4" xr:uid="{00000000-0004-0000-0200-000002000000}"/>
+    <hyperlink ref="C2" location="'Data'!R5C2"/>
+    <hyperlink ref="C3" location="'Data'!R5C3"/>
+    <hyperlink ref="C4" location="'Data'!R5C4"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter>
-    <oddHeader>&amp;C&amp;"Aptos"&amp;10&amp;K000000 UNCLASSIFIED&amp;1#_x000D_</oddHeader>
-    <oddFooter>&amp;C_x000D_&amp;1#&amp;"Aptos"&amp;10&amp;K000000 UNCLASSIFIED</oddFooter>
-  </headerFooter>
 </worksheet>
 </file>